--- a/Demanda diaria salida.xlsx
+++ b/Demanda diaria salida.xlsx
@@ -523,7 +523,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -531,22 +531,22 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>39000</v>
+        <v>11000</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>39000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="3">
@@ -554,7 +554,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -562,22 +562,22 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>77500</v>
+        <v>20000</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>77500</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="4">
@@ -585,7 +585,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -593,22 +593,22 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>114500</v>
+        <v>28500</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>114500</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>150500</v>
+        <v>37000</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>150500</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="6">
@@ -647,7 +647,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -655,22 +655,22 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>185500</v>
+        <v>44000</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>185500</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="7">
@@ -678,7 +678,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>219500</v>
+        <v>50500</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>219500</v>
+        <v>50500</v>
       </c>
     </row>
     <row r="8">
@@ -709,7 +709,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -717,22 +717,22 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>252000</v>
+        <v>56500</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>252000</v>
+        <v>56500</v>
       </c>
     </row>
     <row r="9">
@@ -740,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>283500</v>
+        <v>60500</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>283500</v>
+        <v>65500</v>
       </c>
     </row>
     <row r="10">
@@ -771,7 +771,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -782,19 +782,19 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>314000</v>
+        <v>63500</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>314000</v>
+        <v>68500</v>
       </c>
     </row>
     <row r="11">
@@ -802,7 +802,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -810,22 +810,22 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>344500</v>
+        <v>65000</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>344500</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="12">
@@ -833,7 +833,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -844,19 +844,19 @@
         <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>373500</v>
+        <v>65000</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>373500</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="13">
@@ -864,7 +864,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>401500</v>
+        <v>65000</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>401500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="14">
@@ -895,7 +895,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>429000</v>
+        <v>65000</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>429000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="15">
@@ -926,7 +926,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
@@ -934,22 +934,22 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>454000</v>
+        <v>65000</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>454000</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="16">
@@ -957,7 +957,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
@@ -965,22 +965,22 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>477500</v>
+        <v>65000</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>477500</v>
+        <v>170000</v>
       </c>
     </row>
     <row r="17">
@@ -988,7 +988,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
         <v>2</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>500000</v>
+        <v>65000</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>500000</v>
+        <v>190000</v>
       </c>
     </row>
     <row r="18">
@@ -1019,7 +1019,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
@@ -1027,22 +1027,22 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>522500</v>
+        <v>65000</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>522500</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="19">
@@ -1050,30 +1050,30 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>543500</v>
+        <v>75000</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>543500</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="20">
@@ -1081,7 +1081,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
@@ -1089,22 +1089,22 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>564500</v>
+        <v>83000</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>564500</v>
+        <v>228000</v>
       </c>
     </row>
     <row r="21">
@@ -1112,7 +1112,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         <v>2</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>584500</v>
+        <v>90000</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>584500</v>
+        <v>235000</v>
       </c>
     </row>
     <row r="22">
@@ -1143,7 +1143,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
@@ -1151,22 +1151,22 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>602500</v>
+        <v>97000</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>602500</v>
+        <v>242000</v>
       </c>
     </row>
     <row r="23">
@@ -1174,7 +1174,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
@@ -1182,22 +1182,22 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>619500</v>
+        <v>102500</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>619500</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="24">
@@ -1205,7 +1205,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
@@ -1213,22 +1213,22 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>635500</v>
+        <v>106000</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>635500</v>
+        <v>256000</v>
       </c>
     </row>
     <row r="25">
@@ -1236,7 +1236,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
@@ -1247,19 +1247,19 @@
         <v>2</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>650500</v>
+        <v>108500</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>650500</v>
+        <v>258500</v>
       </c>
     </row>
     <row r="26">
@@ -1267,7 +1267,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
@@ -1275,22 +1275,22 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>665500</v>
+        <v>110500</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>665500</v>
+        <v>260500</v>
       </c>
     </row>
     <row r="27">
@@ -1298,7 +1298,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
@@ -1306,22 +1306,22 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>679000</v>
+        <v>112000</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>679000</v>
+        <v>262000</v>
       </c>
     </row>
     <row r="28">
@@ -1329,7 +1329,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
@@ -1340,19 +1340,19 @@
         <v>2</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>691500</v>
+        <v>112500</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>691500</v>
+        <v>262500</v>
       </c>
     </row>
     <row r="29">
@@ -1360,7 +1360,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>702000</v>
+        <v>112500</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>702000</v>
+        <v>262500</v>
       </c>
     </row>
     <row r="30">
@@ -1391,7 +1391,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
@@ -1399,22 +1399,22 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>710500</v>
+        <v>112500</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>715500</v>
+        <v>282500</v>
       </c>
     </row>
     <row r="31">
@@ -1422,7 +1422,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>716500</v>
+        <v>112500</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>721500</v>
+        <v>302500</v>
       </c>
     </row>
     <row r="32">
@@ -1453,7 +1453,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
@@ -1461,22 +1461,22 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>721500</v>
+        <v>112500</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>726500</v>
+        <v>312500</v>
       </c>
     </row>
     <row r="33">
@@ -1484,30 +1484,30 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>724500</v>
+        <v>121500</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>729500</v>
+        <v>321500</v>
       </c>
     </row>
     <row r="34">
@@ -1515,7 +1515,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>727500</v>
+        <v>130000</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>732500</v>
+        <v>330000</v>
       </c>
     </row>
     <row r="35">
@@ -1546,7 +1546,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>730000</v>
+        <v>137000</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>735000</v>
+        <v>337000</v>
       </c>
     </row>
     <row r="36">
@@ -1577,7 +1577,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
@@ -1585,22 +1585,22 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>731000</v>
+        <v>142000</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>736000</v>
+        <v>347000</v>
       </c>
     </row>
     <row r="37">
@@ -1608,7 +1608,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
@@ -1616,22 +1616,22 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>731000</v>
+        <v>144500</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>736000</v>
+        <v>349500</v>
       </c>
     </row>
     <row r="38">
@@ -1639,7 +1639,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
@@ -1647,22 +1647,22 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>731000</v>
+        <v>145500</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>736000</v>
+        <v>350500</v>
       </c>
     </row>
     <row r="39">
@@ -1670,7 +1670,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>0</v>
@@ -1687,13 +1687,13 @@
         <v>1</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>731000</v>
+        <v>145500</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>40000</v>
+        <v>200000</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>776000</v>
+        <v>360500</v>
       </c>
     </row>
     <row r="40">
@@ -1709,22 +1709,22 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>731000</v>
+        <v>145500</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>80000</v>
+        <v>230000</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>816000</v>
+        <v>390500</v>
       </c>
     </row>
     <row r="41">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>731000</v>
+        <v>145500</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>120000</v>
+        <v>260000</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>856000</v>
+        <v>420500</v>
       </c>
     </row>
     <row r="42">
@@ -1771,22 +1771,22 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>731000</v>
+        <v>145500</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>200000</v>
+        <v>260000</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>936000</v>
+        <v>420500</v>
       </c>
     </row>
     <row r="43">
@@ -1794,30 +1794,30 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>750500</v>
+        <v>145500</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>200000</v>
+        <v>280000</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>955500</v>
+        <v>440500</v>
       </c>
     </row>
     <row r="44">
@@ -1825,30 +1825,30 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>768000</v>
+        <v>156500</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>200000</v>
+        <v>280000</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>973000</v>
+        <v>451500</v>
       </c>
     </row>
     <row r="45">
@@ -1856,7 +1856,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
@@ -1864,22 +1864,22 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>784500</v>
+        <v>167500</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>200000</v>
+        <v>280000</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>989500</v>
+        <v>462500</v>
       </c>
     </row>
     <row r="46">
@@ -1887,7 +1887,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
@@ -1895,22 +1895,22 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>801000</v>
+        <v>177000</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>200000</v>
+        <v>280000</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>1006000</v>
+        <v>472000</v>
       </c>
     </row>
     <row r="47">
@@ -1918,7 +1918,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
@@ -1929,19 +1929,19 @@
         <v>3</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>816000</v>
+        <v>185000</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>200000</v>
+        <v>280000</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>1021000</v>
+        <v>480000</v>
       </c>
     </row>
     <row r="48">
@@ -1949,7 +1949,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
@@ -1957,22 +1957,22 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>829000</v>
+        <v>193000</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>200000</v>
+        <v>280000</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>1034000</v>
+        <v>488000</v>
       </c>
     </row>
     <row r="49">
@@ -1980,7 +1980,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
@@ -1991,19 +1991,19 @@
         <v>2</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>841000</v>
+        <v>200000</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>200000</v>
+        <v>280000</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>1046000</v>
+        <v>495000</v>
       </c>
     </row>
     <row r="50">
@@ -2011,7 +2011,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
@@ -2019,22 +2019,22 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>852500</v>
+        <v>205000</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>200000</v>
+        <v>280000</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>1057500</v>
+        <v>505000</v>
       </c>
     </row>
     <row r="51">
@@ -2042,7 +2042,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
@@ -2053,19 +2053,19 @@
         <v>1</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>863500</v>
+        <v>209500</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>200000</v>
+        <v>280000</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>1068500</v>
+        <v>509500</v>
       </c>
     </row>
     <row r="52">
@@ -2073,7 +2073,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
@@ -2081,22 +2081,22 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>873500</v>
+        <v>212500</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>200000</v>
+        <v>280000</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>1083500</v>
+        <v>512500</v>
       </c>
     </row>
     <row r="53">
@@ -2104,7 +2104,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
@@ -2112,22 +2112,22 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>883000</v>
+        <v>214000</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>200000</v>
+        <v>280000</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>1093000</v>
+        <v>514000</v>
       </c>
     </row>
     <row r="54">
@@ -2135,7 +2135,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
@@ -2143,22 +2143,22 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>891500</v>
+        <v>215000</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>200000</v>
+        <v>280000</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>1101500</v>
+        <v>515000</v>
       </c>
     </row>
     <row r="55">
@@ -2166,7 +2166,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
@@ -2174,22 +2174,22 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>899000</v>
+        <v>215000</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>1109000</v>
+        <v>535000</v>
       </c>
     </row>
     <row r="56">
@@ -2197,7 +2197,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
@@ -2205,22 +2205,22 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>906000</v>
+        <v>215000</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>200000</v>
+        <v>330000</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>1116000</v>
+        <v>565000</v>
       </c>
     </row>
     <row r="57">
@@ -2228,7 +2228,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
@@ -2236,22 +2236,22 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>909500</v>
+        <v>215000</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>200000</v>
+        <v>350000</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>1119500</v>
+        <v>585000</v>
       </c>
     </row>
     <row r="58">
@@ -2259,7 +2259,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
@@ -2267,22 +2267,22 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>912500</v>
+        <v>215000</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>200000</v>
+        <v>370000</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>1122500</v>
+        <v>605000</v>
       </c>
     </row>
     <row r="59">
@@ -2290,7 +2290,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
@@ -2298,22 +2298,22 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>914000</v>
+        <v>215000</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>200000</v>
+        <v>410000</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1124000</v>
+        <v>645000</v>
       </c>
     </row>
     <row r="60">
@@ -2321,7 +2321,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
@@ -2335,16 +2335,16 @@
         <v>0</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>914000</v>
+        <v>215000</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>240000</v>
+        <v>450000</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>1164000</v>
+        <v>685000</v>
       </c>
     </row>
     <row r="61">
@@ -2352,30 +2352,30 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>931500</v>
+        <v>215000</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>240000</v>
+        <v>460000</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>1181500</v>
+        <v>695000</v>
       </c>
     </row>
     <row r="62">
@@ -2383,30 +2383,30 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>947500</v>
+        <v>226500</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>240000</v>
+        <v>460000</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>1197500</v>
+        <v>706500</v>
       </c>
     </row>
     <row r="63">
@@ -2414,7 +2414,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
@@ -2422,22 +2422,22 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>962000</v>
+        <v>237500</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>240000</v>
+        <v>460000</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>1212000</v>
+        <v>717500</v>
       </c>
     </row>
     <row r="64">
@@ -2445,7 +2445,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
@@ -2456,19 +2456,19 @@
         <v>3</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>975000</v>
+        <v>247000</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>240000</v>
+        <v>460000</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>1225000</v>
+        <v>727000</v>
       </c>
     </row>
     <row r="65">
@@ -2476,7 +2476,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
@@ -2484,22 +2484,22 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>986500</v>
+        <v>255500</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>240000</v>
+        <v>460000</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>1236500</v>
+        <v>735500</v>
       </c>
     </row>
     <row r="66">
@@ -2507,7 +2507,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
@@ -2515,22 +2515,22 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>998000</v>
+        <v>263000</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>240000</v>
+        <v>460000</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>1248000</v>
+        <v>743000</v>
       </c>
     </row>
     <row r="67">
@@ -2538,7 +2538,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
@@ -2549,19 +2549,19 @@
         <v>2</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>1008500</v>
+        <v>269500</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>240000</v>
+        <v>460000</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>1258500</v>
+        <v>749500</v>
       </c>
     </row>
     <row r="68">
@@ -2569,7 +2569,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
@@ -2580,19 +2580,19 @@
         <v>3</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>1017500</v>
+        <v>274500</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>240000</v>
+        <v>460000</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>1272500</v>
+        <v>759500</v>
       </c>
     </row>
     <row r="69">
@@ -2600,7 +2600,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
@@ -2608,22 +2608,22 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>1026500</v>
+        <v>278500</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>240000</v>
+        <v>460000</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>1281500</v>
+        <v>763500</v>
       </c>
     </row>
     <row r="70">
@@ -2631,7 +2631,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
@@ -2639,22 +2639,22 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>1034000</v>
+        <v>281500</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>240000</v>
+        <v>460000</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>1289000</v>
+        <v>766500</v>
       </c>
     </row>
     <row r="71">
@@ -2662,7 +2662,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
@@ -2670,22 +2670,22 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>1040000</v>
+        <v>284500</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>240000</v>
+        <v>460000</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>1295000</v>
+        <v>769500</v>
       </c>
     </row>
     <row r="72">
@@ -2693,7 +2693,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
@@ -2701,22 +2701,22 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>1046000</v>
+        <v>286000</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>240000</v>
+        <v>460000</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>1301000</v>
+        <v>771000</v>
       </c>
     </row>
     <row r="73">
@@ -2724,7 +2724,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
@@ -2735,19 +2735,19 @@
         <v>2</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>1051000</v>
+        <v>286500</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>240000</v>
+        <v>460000</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>1306000</v>
+        <v>771500</v>
       </c>
     </row>
     <row r="74">
@@ -2755,7 +2755,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
@@ -2763,22 +2763,22 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>1054000</v>
+        <v>286500</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>240000</v>
+        <v>460000</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>1309000</v>
+        <v>771500</v>
       </c>
     </row>
     <row r="75">
@@ -2786,7 +2786,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
@@ -2794,22 +2794,22 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F75" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G75" s="4" t="n">
-        <v>1056500</v>
+        <v>286500</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>240000</v>
+        <v>510000</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>1311500</v>
+        <v>821500</v>
       </c>
     </row>
     <row r="76">
@@ -2817,7 +2817,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
@@ -2828,19 +2828,19 @@
         <v>3</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>1057500</v>
+        <v>286500</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>240000</v>
+        <v>540000</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>1312500</v>
+        <v>851500</v>
       </c>
     </row>
     <row r="77">
@@ -2848,7 +2848,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
@@ -2856,22 +2856,22 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>1057500</v>
+        <v>286500</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>280000</v>
+        <v>560000</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>1352500</v>
+        <v>871500</v>
       </c>
     </row>
     <row r="78">
@@ -2887,22 +2887,22 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>1057500</v>
+        <v>286500</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>320000</v>
+        <v>560000</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>1392500</v>
+        <v>871500</v>
       </c>
     </row>
     <row r="79">
@@ -2918,22 +2918,22 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>1057500</v>
+        <v>286500</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>480000</v>
+        <v>590000</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>1552500</v>
+        <v>901500</v>
       </c>
     </row>
     <row r="80">
@@ -2941,7 +2941,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
@@ -2949,22 +2949,22 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>1076000</v>
+        <v>299000</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>480000</v>
+        <v>590000</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>1571000</v>
+        <v>914000</v>
       </c>
     </row>
     <row r="81">
@@ -2972,7 +2972,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
@@ -2983,19 +2983,19 @@
         <v>2</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>1093500</v>
+        <v>310500</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>480000</v>
+        <v>590000</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>1588500</v>
+        <v>925500</v>
       </c>
     </row>
     <row r="82">
@@ -3003,7 +3003,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
@@ -3011,22 +3011,22 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>1110000</v>
+        <v>320000</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>480000</v>
+        <v>590000</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>1605000</v>
+        <v>935000</v>
       </c>
     </row>
     <row r="83">
@@ -3034,7 +3034,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
@@ -3042,22 +3042,22 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>1124500</v>
+        <v>328500</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>480000</v>
+        <v>590000</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>1619500</v>
+        <v>943500</v>
       </c>
     </row>
     <row r="84">
@@ -3065,7 +3065,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
@@ -3073,22 +3073,22 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>1137000</v>
+        <v>336000</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>480000</v>
+        <v>590000</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>1632000</v>
+        <v>951000</v>
       </c>
     </row>
     <row r="85">
@@ -3096,7 +3096,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
@@ -3104,22 +3104,22 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>1149000</v>
+        <v>342500</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>480000</v>
+        <v>590000</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>1644000</v>
+        <v>957500</v>
       </c>
     </row>
     <row r="86">
@@ -3127,7 +3127,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
@@ -3135,22 +3135,22 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>1160000</v>
+        <v>349000</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>480000</v>
+        <v>590000</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>1655000</v>
+        <v>964000</v>
       </c>
     </row>
     <row r="87">
@@ -3158,7 +3158,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
@@ -3166,22 +3166,22 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>1170500</v>
+        <v>354000</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>480000</v>
+        <v>590000</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>1665500</v>
+        <v>974000</v>
       </c>
     </row>
     <row r="88">
@@ -3189,7 +3189,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
@@ -3197,22 +3197,22 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>1179500</v>
+        <v>358000</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>480000</v>
+        <v>590000</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>1679500</v>
+        <v>978000</v>
       </c>
     </row>
     <row r="89">
@@ -3220,7 +3220,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
@@ -3228,22 +3228,22 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>1187500</v>
+        <v>360000</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>480000</v>
+        <v>590000</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>1687500</v>
+        <v>980000</v>
       </c>
     </row>
     <row r="90">
@@ -3251,7 +3251,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
@@ -3259,22 +3259,22 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>1194500</v>
+        <v>360000</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>480000</v>
+        <v>590000</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>1694500</v>
+        <v>980000</v>
       </c>
     </row>
     <row r="91">
@@ -3282,7 +3282,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
@@ -3290,22 +3290,22 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>1200500</v>
+        <v>360000</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>480000</v>
+        <v>640000</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>1700500</v>
+        <v>1030000</v>
       </c>
     </row>
     <row r="92">
@@ -3313,7 +3313,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
@@ -3321,22 +3321,22 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>1205000</v>
+        <v>360000</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>480000</v>
+        <v>660000</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>1705000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="93">
@@ -3344,7 +3344,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
@@ -3352,22 +3352,22 @@
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>1208500</v>
+        <v>360000</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>480000</v>
+        <v>700000</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>1708500</v>
+        <v>1090000</v>
       </c>
     </row>
     <row r="94">
@@ -3375,7 +3375,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
@@ -3383,22 +3383,22 @@
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>1211000</v>
+        <v>360000</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>480000</v>
+        <v>700000</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>1711000</v>
+        <v>1090000</v>
       </c>
     </row>
     <row r="95">
@@ -3406,7 +3406,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
@@ -3414,22 +3414,22 @@
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>1213500</v>
+        <v>360000</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>480000</v>
+        <v>710000</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>1713500</v>
+        <v>1100000</v>
       </c>
     </row>
     <row r="96">
@@ -3437,7 +3437,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
@@ -3448,19 +3448,19 @@
         <v>3</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>1214500</v>
+        <v>360000</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>1714500</v>
+        <v>1130000</v>
       </c>
     </row>
     <row r="97">
@@ -3468,7 +3468,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
@@ -3479,19 +3479,19 @@
         <v>2</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="F97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>1234500</v>
+        <v>371500</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>1734500</v>
+        <v>1141500</v>
       </c>
     </row>
     <row r="98">
@@ -3499,7 +3499,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>1254000</v>
+        <v>383000</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>1754000</v>
+        <v>1153000</v>
       </c>
     </row>
     <row r="99">
@@ -3530,7 +3530,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
@@ -3538,22 +3538,22 @@
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>1271000</v>
+        <v>394000</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>1771000</v>
+        <v>1164000</v>
       </c>
     </row>
     <row r="100">
@@ -3561,7 +3561,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
@@ -3569,22 +3569,22 @@
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>1286500</v>
+        <v>404500</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>1786500</v>
+        <v>1174500</v>
       </c>
     </row>
     <row r="101">
@@ -3592,7 +3592,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
@@ -3600,22 +3600,22 @@
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>1301000</v>
+        <v>414500</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>1801000</v>
+        <v>1184500</v>
       </c>
     </row>
     <row r="102">
@@ -3623,7 +3623,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
@@ -3631,22 +3631,22 @@
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>1315500</v>
+        <v>423500</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>1815500</v>
+        <v>1193500</v>
       </c>
     </row>
     <row r="103">
@@ -3654,7 +3654,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
@@ -3662,22 +3662,22 @@
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>1328500</v>
+        <v>432000</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>1828500</v>
+        <v>1202000</v>
       </c>
     </row>
     <row r="104">
@@ -3685,7 +3685,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
@@ -3693,22 +3693,22 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>1341500</v>
+        <v>438500</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>1841500</v>
+        <v>1208500</v>
       </c>
     </row>
     <row r="105">
@@ -3716,7 +3716,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
@@ -3727,19 +3727,19 @@
         <v>2</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>1353500</v>
+        <v>444000</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>1853500</v>
+        <v>1214000</v>
       </c>
     </row>
     <row r="106">
@@ -3747,7 +3747,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
@@ -3755,22 +3755,22 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>1363500</v>
+        <v>449500</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>1868500</v>
+        <v>1219500</v>
       </c>
     </row>
     <row r="107">
@@ -3778,7 +3778,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
@@ -3786,22 +3786,22 @@
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>1372500</v>
+        <v>453500</v>
       </c>
       <c r="H107" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>1877500</v>
+        <v>1228500</v>
       </c>
     </row>
     <row r="108">
@@ -3809,7 +3809,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
@@ -3817,22 +3817,22 @@
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>1380500</v>
+        <v>455500</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>1885500</v>
+        <v>1230500</v>
       </c>
     </row>
     <row r="109">
@@ -3840,7 +3840,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
@@ -3851,19 +3851,19 @@
         <v>2</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>1387500</v>
+        <v>456500</v>
       </c>
       <c r="H109" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>1892500</v>
+        <v>1231500</v>
       </c>
     </row>
     <row r="110">
@@ -3871,7 +3871,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
@@ -3879,22 +3879,22 @@
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>1394500</v>
+        <v>457000</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>1899500</v>
+        <v>1232000</v>
       </c>
     </row>
     <row r="111">
@@ -3902,7 +3902,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
@@ -3910,22 +3910,22 @@
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>1400000</v>
+        <v>457000</v>
       </c>
       <c r="H111" s="4" t="n">
-        <v>480000</v>
+        <v>740000</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>1905000</v>
+        <v>1232000</v>
       </c>
     </row>
     <row r="112">
@@ -3933,7 +3933,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
@@ -3944,19 +3944,19 @@
         <v>2</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>1404500</v>
+        <v>457000</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>480000</v>
+        <v>760000</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>1909500</v>
+        <v>1252000</v>
       </c>
     </row>
     <row r="113">
@@ -3964,7 +3964,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
@@ -3972,22 +3972,22 @@
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>1407000</v>
+        <v>457000</v>
       </c>
       <c r="H113" s="4" t="n">
-        <v>480000</v>
+        <v>770000</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>1912000</v>
+        <v>1262000</v>
       </c>
     </row>
     <row r="114">
@@ -3995,7 +3995,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
@@ -4003,22 +4003,22 @@
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>1407500</v>
+        <v>457000</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>480000</v>
+        <v>790000</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>1912500</v>
+        <v>1282000</v>
       </c>
     </row>
     <row r="115">
@@ -4026,7 +4026,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
@@ -4034,22 +4034,22 @@
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>1407500</v>
+        <v>457000</v>
       </c>
       <c r="H115" s="4" t="n">
-        <v>640000</v>
+        <v>810000</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>2072500</v>
+        <v>1302000</v>
       </c>
     </row>
     <row r="116">
@@ -4057,30 +4057,30 @@
         <v>115</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>1407500</v>
+        <v>469000</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>720000</v>
+        <v>810000</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>2152500</v>
+        <v>1314000</v>
       </c>
     </row>
     <row r="117">
@@ -4088,7 +4088,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
@@ -4096,22 +4096,22 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>1407500</v>
+        <v>477500</v>
       </c>
       <c r="H117" s="4" t="n">
-        <v>880000</v>
+        <v>810000</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>2312500</v>
+        <v>1322500</v>
       </c>
     </row>
     <row r="118">
@@ -4119,7 +4119,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
@@ -4127,22 +4127,22 @@
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>1407500</v>
+        <v>485500</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>880000</v>
+        <v>810000</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>2312500</v>
+        <v>1330500</v>
       </c>
     </row>
     <row r="119">
@@ -4150,7 +4150,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
@@ -4158,22 +4158,22 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>1407500</v>
+        <v>492000</v>
       </c>
       <c r="H119" s="4" t="n">
-        <v>920000</v>
+        <v>810000</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>2352500</v>
+        <v>1337000</v>
       </c>
     </row>
     <row r="120">
@@ -4181,30 +4181,30 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>1426000</v>
+        <v>496500</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>920000</v>
+        <v>810000</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>2371000</v>
+        <v>1346500</v>
       </c>
     </row>
     <row r="121">
@@ -4212,7 +4212,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
@@ -4220,22 +4220,22 @@
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>1443500</v>
+        <v>498500</v>
       </c>
       <c r="H121" s="4" t="n">
-        <v>920000</v>
+        <v>810000</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>2388500</v>
+        <v>1348500</v>
       </c>
     </row>
     <row r="122">
@@ -4243,7 +4243,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
@@ -4251,22 +4251,22 @@
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="F122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>1461000</v>
+        <v>499000</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>920000</v>
+        <v>810000</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>2406000</v>
+        <v>1349000</v>
       </c>
     </row>
     <row r="123">
@@ -4274,7 +4274,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
@@ -4282,22 +4282,22 @@
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>1478000</v>
+        <v>499000</v>
       </c>
       <c r="H123" s="4" t="n">
-        <v>920000</v>
+        <v>830000</v>
       </c>
       <c r="I123" s="4" t="n">
-        <v>2423000</v>
+        <v>1369000</v>
       </c>
     </row>
     <row r="124">
@@ -4305,7 +4305,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
@@ -4313,22 +4313,22 @@
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>1494500</v>
+        <v>499000</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>920000</v>
+        <v>860000</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>2439500</v>
+        <v>1399000</v>
       </c>
     </row>
     <row r="125">
@@ -4336,7 +4336,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
@@ -4344,22 +4344,22 @@
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>1510500</v>
+        <v>499000</v>
       </c>
       <c r="H125" s="4" t="n">
-        <v>920000</v>
+        <v>890000</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>2455500</v>
+        <v>1429000</v>
       </c>
     </row>
     <row r="126">
@@ -4367,7 +4367,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
@@ -4375,22 +4375,22 @@
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>1525500</v>
+        <v>499000</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>920000</v>
+        <v>890000</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>2470500</v>
+        <v>1429000</v>
       </c>
     </row>
     <row r="127">
@@ -4398,7 +4398,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
@@ -4406,22 +4406,22 @@
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>1540000</v>
+        <v>499000</v>
       </c>
       <c r="H127" s="4" t="n">
-        <v>920000</v>
+        <v>910000</v>
       </c>
       <c r="I127" s="4" t="n">
-        <v>2485000</v>
+        <v>1449000</v>
       </c>
     </row>
     <row r="128">
@@ -4429,7 +4429,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
@@ -4437,22 +4437,22 @@
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>1552500</v>
+        <v>499000</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>920000</v>
+        <v>940000</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>2497500</v>
+        <v>1479000</v>
       </c>
     </row>
     <row r="129">
@@ -4460,7 +4460,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
@@ -4468,22 +4468,22 @@
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F129" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>1564000</v>
+        <v>499000</v>
       </c>
       <c r="H129" s="4" t="n">
-        <v>920000</v>
+        <v>940000</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>2509000</v>
+        <v>1479000</v>
       </c>
     </row>
     <row r="130">
@@ -4491,7 +4491,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
@@ -4499,22 +4499,22 @@
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>1575500</v>
+        <v>499000</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>920000</v>
+        <v>970000</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>2520500</v>
+        <v>1509000</v>
       </c>
     </row>
     <row r="131">
@@ -4522,7 +4522,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
@@ -4533,19 +4533,19 @@
         <v>3</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>1585500</v>
+        <v>499000</v>
       </c>
       <c r="H131" s="4" t="n">
-        <v>920000</v>
+        <v>1000000</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>2535500</v>
+        <v>1539000</v>
       </c>
     </row>
     <row r="132">
@@ -4553,30 +4553,30 @@
         <v>131</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F132" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>1593500</v>
+        <v>511500</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>920000</v>
+        <v>1000000</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>2543500</v>
+        <v>1551500</v>
       </c>
     </row>
     <row r="133">
@@ -4584,7 +4584,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
@@ -4595,19 +4595,19 @@
         <v>2</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F133" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>1600500</v>
+        <v>523000</v>
       </c>
       <c r="H133" s="4" t="n">
-        <v>920000</v>
+        <v>1000000</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>2550500</v>
+        <v>1563000</v>
       </c>
     </row>
     <row r="134">
@@ -4615,7 +4615,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
@@ -4623,22 +4623,22 @@
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F134" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>1607000</v>
+        <v>532500</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>920000</v>
+        <v>1000000</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>2557000</v>
+        <v>1572500</v>
       </c>
     </row>
     <row r="135">
@@ -4646,7 +4646,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
@@ -4657,19 +4657,19 @@
         <v>1</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F135" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>1613000</v>
+        <v>541500</v>
       </c>
       <c r="H135" s="4" t="n">
-        <v>920000</v>
+        <v>1000000</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>2563000</v>
+        <v>1581500</v>
       </c>
     </row>
     <row r="136">
@@ -4677,7 +4677,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
@@ -4685,22 +4685,22 @@
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>1618000</v>
+        <v>549000</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>920000</v>
+        <v>1000000</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>2568000</v>
+        <v>1589000</v>
       </c>
     </row>
     <row r="137">
@@ -4708,7 +4708,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
@@ -4716,22 +4716,22 @@
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F137" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>1622500</v>
+        <v>555000</v>
       </c>
       <c r="H137" s="4" t="n">
-        <v>920000</v>
+        <v>1000000</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>2572500</v>
+        <v>1595000</v>
       </c>
     </row>
     <row r="138">
@@ -4739,7 +4739,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
@@ -4747,22 +4747,22 @@
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F138" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>1626000</v>
+        <v>560500</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>920000</v>
+        <v>1000000</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>2576000</v>
+        <v>1600500</v>
       </c>
     </row>
     <row r="139">
@@ -4770,30 +4770,30 @@
         <v>138</v>
       </c>
       <c r="B139" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E139" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E139" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="F139" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>1628500</v>
+        <v>564000</v>
       </c>
       <c r="H139" s="4" t="n">
-        <v>920000</v>
+        <v>1000000</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>2578500</v>
+        <v>1609000</v>
       </c>
     </row>
     <row r="140">
@@ -4801,7 +4801,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E140" s="2" t="n">
         <v>4</v>
@@ -4818,13 +4818,13 @@
         <v>0</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>1630500</v>
+        <v>566000</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>920000</v>
+        <v>1000000</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>2580500</v>
+        <v>1611000</v>
       </c>
     </row>
     <row r="141">
@@ -4840,22 +4840,22 @@
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>1630500</v>
+        <v>567000</v>
       </c>
       <c r="H141" s="4" t="n">
-        <v>1040000</v>
+        <v>1000000</v>
       </c>
       <c r="I141" s="4" t="n">
-        <v>2700500</v>
+        <v>1612000</v>
       </c>
     </row>
     <row r="142">
@@ -4863,7 +4863,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
@@ -4871,22 +4871,22 @@
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>1630500</v>
+        <v>567000</v>
       </c>
       <c r="H142" s="4" t="n">
-        <v>1080000</v>
+        <v>1000000</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>2740500</v>
+        <v>1612000</v>
       </c>
     </row>
     <row r="143">
@@ -4902,22 +4902,22 @@
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>1630500</v>
+        <v>567000</v>
       </c>
       <c r="H143" s="4" t="n">
-        <v>1200000</v>
+        <v>1040000</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>2860500</v>
+        <v>1652000</v>
       </c>
     </row>
     <row r="144">
@@ -4942,13 +4942,13 @@
         <v>4</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>1630500</v>
+        <v>567000</v>
       </c>
       <c r="H144" s="4" t="n">
-        <v>1360000</v>
+        <v>1080000</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>3020500</v>
+        <v>1692000</v>
       </c>
     </row>
     <row r="145">
@@ -4956,30 +4956,30 @@
         <v>144</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>1648000</v>
+        <v>567000</v>
       </c>
       <c r="H145" s="4" t="n">
-        <v>1360000</v>
+        <v>1090000</v>
       </c>
       <c r="I145" s="4" t="n">
-        <v>3038000</v>
+        <v>1702000</v>
       </c>
     </row>
     <row r="146">
@@ -4987,7 +4987,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
@@ -4995,22 +4995,22 @@
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>1664000</v>
+        <v>567000</v>
       </c>
       <c r="H146" s="4" t="n">
-        <v>1360000</v>
+        <v>1110000</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>3054000</v>
+        <v>1722000</v>
       </c>
     </row>
     <row r="147">
@@ -5018,7 +5018,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
@@ -5026,22 +5026,22 @@
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>1678500</v>
+        <v>567000</v>
       </c>
       <c r="H147" s="4" t="n">
-        <v>1360000</v>
+        <v>1120000</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>3068500</v>
+        <v>1732000</v>
       </c>
     </row>
     <row r="148">
@@ -5049,7 +5049,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
@@ -5060,19 +5060,19 @@
         <v>3</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>1691500</v>
+        <v>567000</v>
       </c>
       <c r="H148" s="4" t="n">
-        <v>1360000</v>
+        <v>1150000</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>3081500</v>
+        <v>1762000</v>
       </c>
     </row>
     <row r="149">
@@ -5080,7 +5080,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
@@ -5088,22 +5088,22 @@
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>1703000</v>
+        <v>567000</v>
       </c>
       <c r="H149" s="4" t="n">
-        <v>1360000</v>
+        <v>1170000</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>3093000</v>
+        <v>1782000</v>
       </c>
     </row>
     <row r="150">
@@ -5111,15 +5111,15 @@
         <v>149</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E150" s="2" t="n">
         <v>23</v>
@@ -5128,13 +5128,13 @@
         <v>0</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>1714500</v>
+        <v>578500</v>
       </c>
       <c r="H150" s="4" t="n">
-        <v>1360000</v>
+        <v>1170000</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>3104500</v>
+        <v>1793500</v>
       </c>
     </row>
     <row r="151">
@@ -5159,13 +5159,13 @@
         <v>0</v>
       </c>
       <c r="G151" s="4" t="n">
-        <v>1725000</v>
+        <v>589000</v>
       </c>
       <c r="H151" s="4" t="n">
-        <v>1360000</v>
+        <v>1170000</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>3115000</v>
+        <v>1804000</v>
       </c>
     </row>
     <row r="152">
@@ -5190,13 +5190,13 @@
         <v>0</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>1734000</v>
+        <v>598000</v>
       </c>
       <c r="H152" s="4" t="n">
-        <v>1360000</v>
+        <v>1170000</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>3129000</v>
+        <v>1813000</v>
       </c>
     </row>
     <row r="153">
@@ -5212,22 +5212,22 @@
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>1743000</v>
+        <v>606000</v>
       </c>
       <c r="H153" s="4" t="n">
-        <v>1360000</v>
+        <v>1170000</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>3138000</v>
+        <v>1821000</v>
       </c>
     </row>
     <row r="154">
@@ -5235,7 +5235,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
@@ -5243,22 +5243,22 @@
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>1750500</v>
+        <v>613000</v>
       </c>
       <c r="H154" s="4" t="n">
-        <v>1360000</v>
+        <v>1170000</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>3145500</v>
+        <v>1828000</v>
       </c>
     </row>
     <row r="155">
@@ -5266,7 +5266,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
@@ -5274,22 +5274,22 @@
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F155" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>1756500</v>
+        <v>620000</v>
       </c>
       <c r="H155" s="4" t="n">
-        <v>1360000</v>
+        <v>1170000</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>3151500</v>
+        <v>1835000</v>
       </c>
     </row>
     <row r="156">
@@ -5297,7 +5297,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
@@ -5305,22 +5305,22 @@
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>1762500</v>
+        <v>625500</v>
       </c>
       <c r="H156" s="4" t="n">
-        <v>1360000</v>
+        <v>1170000</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>3157500</v>
+        <v>1840500</v>
       </c>
     </row>
     <row r="157">
@@ -5328,7 +5328,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
@@ -5339,19 +5339,19 @@
         <v>2</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F157" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>1767500</v>
+        <v>630000</v>
       </c>
       <c r="H157" s="4" t="n">
-        <v>1360000</v>
+        <v>1170000</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>3162500</v>
+        <v>1850000</v>
       </c>
     </row>
     <row r="158">
@@ -5359,7 +5359,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
@@ -5367,22 +5367,22 @@
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F158" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>1770500</v>
+        <v>634000</v>
       </c>
       <c r="H158" s="4" t="n">
-        <v>1360000</v>
+        <v>1170000</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>3165500</v>
+        <v>1854000</v>
       </c>
     </row>
     <row r="159">
@@ -5390,7 +5390,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
@@ -5398,22 +5398,22 @@
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F159" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>1773000</v>
+        <v>635500</v>
       </c>
       <c r="H159" s="4" t="n">
-        <v>1360000</v>
+        <v>1170000</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>3168000</v>
+        <v>1855500</v>
       </c>
     </row>
     <row r="160">
@@ -5421,7 +5421,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
@@ -5432,19 +5432,19 @@
         <v>3</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F160" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>1774000</v>
+        <v>635500</v>
       </c>
       <c r="H160" s="4" t="n">
-        <v>1360000</v>
+        <v>1170000</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>3169000</v>
+        <v>1855500</v>
       </c>
     </row>
     <row r="161">
@@ -5452,7 +5452,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
@@ -5460,22 +5460,22 @@
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E161" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>1774000</v>
+        <v>635500</v>
       </c>
       <c r="H161" s="4" t="n">
-        <v>1400000</v>
+        <v>1190000</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>3209000</v>
+        <v>1875500</v>
       </c>
     </row>
     <row r="162">
@@ -5483,30 +5483,30 @@
         <v>161</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>1793500</v>
+        <v>635500</v>
       </c>
       <c r="H162" s="4" t="n">
-        <v>1400000</v>
+        <v>1190000</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>3228500</v>
+        <v>1875500</v>
       </c>
     </row>
     <row r="163">
@@ -5514,7 +5514,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
@@ -5522,22 +5522,22 @@
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>1811000</v>
+        <v>635500</v>
       </c>
       <c r="H163" s="4" t="n">
-        <v>1400000</v>
+        <v>1220000</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>3246000</v>
+        <v>1905500</v>
       </c>
     </row>
     <row r="164">
@@ -5545,7 +5545,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
@@ -5553,22 +5553,22 @@
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F164" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>1827000</v>
+        <v>635500</v>
       </c>
       <c r="H164" s="4" t="n">
-        <v>1400000</v>
+        <v>1220000</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>3262000</v>
+        <v>1905500</v>
       </c>
     </row>
     <row r="165">
@@ -5576,7 +5576,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
@@ -5587,19 +5587,19 @@
         <v>2</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F165" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G165" s="4" t="n">
-        <v>1842000</v>
+        <v>635500</v>
       </c>
       <c r="H165" s="4" t="n">
-        <v>1400000</v>
+        <v>1240000</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>3277000</v>
+        <v>1925500</v>
       </c>
     </row>
     <row r="166">
@@ -5607,7 +5607,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
@@ -5615,22 +5615,22 @@
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>1856000</v>
+        <v>635500</v>
       </c>
       <c r="H166" s="4" t="n">
-        <v>1400000</v>
+        <v>1280000</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>3291000</v>
+        <v>1965500</v>
       </c>
     </row>
     <row r="167">
@@ -5638,7 +5638,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
@@ -5646,22 +5646,22 @@
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>1868000</v>
+        <v>635500</v>
       </c>
       <c r="H167" s="4" t="n">
-        <v>1400000</v>
+        <v>1300000</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>3303000</v>
+        <v>1985500</v>
       </c>
     </row>
     <row r="168">
@@ -5669,7 +5669,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
@@ -5677,22 +5677,22 @@
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F168" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>1878000</v>
+        <v>635500</v>
       </c>
       <c r="H168" s="4" t="n">
-        <v>1400000</v>
+        <v>1320000</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>3318000</v>
+        <v>2005500</v>
       </c>
     </row>
     <row r="169">
@@ -5700,30 +5700,30 @@
         <v>168</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F169" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>1887500</v>
+        <v>647000</v>
       </c>
       <c r="H169" s="4" t="n">
-        <v>1400000</v>
+        <v>1320000</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>3327500</v>
+        <v>2017000</v>
       </c>
     </row>
     <row r="170">
@@ -5731,7 +5731,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
@@ -5739,22 +5739,22 @@
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F170" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>1896000</v>
+        <v>658500</v>
       </c>
       <c r="H170" s="4" t="n">
-        <v>1400000</v>
+        <v>1320000</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>3336000</v>
+        <v>2028500</v>
       </c>
     </row>
     <row r="171">
@@ -5762,7 +5762,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
@@ -5770,22 +5770,22 @@
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F171" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G171" s="4" t="n">
-        <v>1904000</v>
+        <v>668500</v>
       </c>
       <c r="H171" s="4" t="n">
-        <v>1400000</v>
+        <v>1320000</v>
       </c>
       <c r="I171" s="4" t="n">
-        <v>3344000</v>
+        <v>2038500</v>
       </c>
     </row>
     <row r="172">
@@ -5793,7 +5793,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F172" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>1910500</v>
+        <v>677500</v>
       </c>
       <c r="H172" s="4" t="n">
-        <v>1400000</v>
+        <v>1320000</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>3350500</v>
+        <v>2047500</v>
       </c>
     </row>
     <row r="173">
@@ -5824,7 +5824,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
@@ -5832,22 +5832,22 @@
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F173" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G173" s="4" t="n">
-        <v>1916000</v>
+        <v>684500</v>
       </c>
       <c r="H173" s="4" t="n">
-        <v>1400000</v>
+        <v>1320000</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>3356000</v>
+        <v>2054500</v>
       </c>
     </row>
     <row r="174">
@@ -5855,7 +5855,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
@@ -5863,22 +5863,22 @@
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F174" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>1920500</v>
+        <v>689500</v>
       </c>
       <c r="H174" s="4" t="n">
-        <v>1400000</v>
+        <v>1320000</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>3360500</v>
+        <v>2064500</v>
       </c>
     </row>
     <row r="175">
@@ -5886,7 +5886,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
@@ -5894,22 +5894,22 @@
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F175" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G175" s="4" t="n">
-        <v>1924000</v>
+        <v>692000</v>
       </c>
       <c r="H175" s="4" t="n">
-        <v>1400000</v>
+        <v>1320000</v>
       </c>
       <c r="I175" s="4" t="n">
-        <v>3364000</v>
+        <v>2067000</v>
       </c>
     </row>
     <row r="176">
@@ -5917,7 +5917,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
@@ -5925,22 +5925,22 @@
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F176" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G176" s="4" t="n">
-        <v>1926000</v>
+        <v>693500</v>
       </c>
       <c r="H176" s="4" t="n">
-        <v>1400000</v>
+        <v>1320000</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>3366000</v>
+        <v>2068500</v>
       </c>
     </row>
     <row r="177">
@@ -5948,30 +5948,30 @@
         <v>176</v>
       </c>
       <c r="B177" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="E177" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F177" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" s="4" t="n">
-        <v>1927000</v>
+        <v>693500</v>
       </c>
       <c r="H177" s="4" t="n">
-        <v>1400000</v>
+        <v>1330000</v>
       </c>
       <c r="I177" s="4" t="n">
-        <v>3367000</v>
+        <v>2078500</v>
       </c>
     </row>
     <row r="178">
@@ -5979,7 +5979,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E178" s="2" t="n">
         <v>0</v>
@@ -5996,13 +5996,13 @@
         <v>0</v>
       </c>
       <c r="G178" s="4" t="n">
-        <v>1927000</v>
+        <v>693500</v>
       </c>
       <c r="H178" s="4" t="n">
-        <v>1400000</v>
+        <v>1330000</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>3367000</v>
+        <v>2078500</v>
       </c>
     </row>
     <row r="179">
@@ -6018,22 +6018,22 @@
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E179" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F179" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G179" s="4" t="n">
-        <v>1927000</v>
+        <v>693500</v>
       </c>
       <c r="H179" s="4" t="n">
-        <v>1400000</v>
+        <v>1340000</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>3367000</v>
+        <v>2088500</v>
       </c>
     </row>
     <row r="180">
@@ -6058,13 +6058,13 @@
         <v>3</v>
       </c>
       <c r="G180" s="4" t="n">
-        <v>1927000</v>
+        <v>693500</v>
       </c>
       <c r="H180" s="4" t="n">
-        <v>1520000</v>
+        <v>1370000</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>3487000</v>
+        <v>2118500</v>
       </c>
     </row>
     <row r="181">
@@ -6072,30 +6072,30 @@
         <v>180</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F181" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G181" s="4" t="n">
-        <v>1927000</v>
+        <v>705000</v>
       </c>
       <c r="H181" s="4" t="n">
-        <v>1600000</v>
+        <v>1370000</v>
       </c>
       <c r="I181" s="4" t="n">
-        <v>3567000</v>
+        <v>2130000</v>
       </c>
     </row>
   </sheetData>
